--- a/data/participant_sample.xlsx
+++ b/data/participant_sample.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cristina\repos\ei_maps\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D402601-C8C9-46C8-BEF0-FF793DAC7637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72B1D60-A044-48E4-851E-0CC665761E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30255" yWindow="4395" windowWidth="21600" windowHeight="11295" xr2:uid="{A8CE7551-8922-47F6-B549-E6B85DA15C6C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A8CE7551-8922-47F6-B549-E6B85DA15C6C}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$A$1:$T$730</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$F$1:$F$730</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
@@ -6674,7 +6674,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -6682,7 +6682,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -22648,7 +22647,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FAB02E2-8283-44DB-BC1E-88DE8C1F843E}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:T730"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -22732,7 +22730,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2179</v>
       </c>
@@ -22778,7 +22776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2179</v>
       </c>
@@ -22836,7 +22834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2179</v>
       </c>
@@ -22894,7 +22892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2179</v>
       </c>
@@ -22952,7 +22950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2179</v>
       </c>
@@ -23010,7 +23008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>2179</v>
       </c>
@@ -23068,7 +23066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2179</v>
       </c>
@@ -23126,7 +23124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2179</v>
       </c>
@@ -23184,7 +23182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>2179</v>
       </c>
@@ -23242,7 +23240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>2179</v>
       </c>
@@ -23300,7 +23298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>2179</v>
       </c>
@@ -23358,7 +23356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>2179</v>
       </c>
@@ -23416,7 +23414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>2179</v>
       </c>
@@ -23474,7 +23472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>2179</v>
       </c>
@@ -23532,7 +23530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>2179</v>
       </c>
@@ -23590,7 +23588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>2179</v>
       </c>
@@ -23648,7 +23646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>2179</v>
       </c>
@@ -23706,7 +23704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>2179</v>
       </c>
@@ -23764,7 +23762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>2179</v>
       </c>
@@ -23822,7 +23820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>2179</v>
       </c>
@@ -23877,7 +23875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>2179</v>
       </c>
@@ -23935,7 +23933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>2179</v>
       </c>
@@ -23993,7 +23991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>2179</v>
       </c>
@@ -24045,7 +24043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>2179</v>
       </c>
@@ -24097,7 +24095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>2179</v>
       </c>
@@ -24155,7 +24153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>2179</v>
       </c>
@@ -24213,7 +24211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>2179</v>
       </c>
@@ -24271,7 +24269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>2179</v>
       </c>
@@ -24329,7 +24327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>2179</v>
       </c>
@@ -24387,7 +24385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>2179</v>
       </c>
@@ -24445,7 +24443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>2179</v>
       </c>
@@ -24503,7 +24501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>2179</v>
       </c>
@@ -24561,7 +24559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>2179</v>
       </c>
@@ -24607,7 +24605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>2179</v>
       </c>
@@ -24665,7 +24663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>2179</v>
       </c>
@@ -24723,7 +24721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>2179</v>
       </c>
@@ -24781,7 +24779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>2179</v>
       </c>
@@ -24839,7 +24837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>2179</v>
       </c>
@@ -24897,7 +24895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>2179</v>
       </c>
@@ -24955,7 +24953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>2179</v>
       </c>
@@ -25013,7 +25011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>2179</v>
       </c>
@@ -25071,7 +25069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>2179</v>
       </c>
@@ -25123,7 +25121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>2179</v>
       </c>
@@ -25181,7 +25179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>2179</v>
       </c>
@@ -25239,7 +25237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>2179</v>
       </c>
@@ -25297,7 +25295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>2179</v>
       </c>
@@ -25355,7 +25353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>2179</v>
       </c>
@@ -25413,7 +25411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>2179</v>
       </c>
@@ -25459,7 +25457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>2179</v>
       </c>
@@ -25517,7 +25515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>2179</v>
       </c>
@@ -25575,7 +25573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>2179</v>
       </c>
@@ -25633,7 +25631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>2179</v>
       </c>
@@ -25691,7 +25689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>2179</v>
       </c>
@@ -25749,7 +25747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>2179</v>
       </c>
@@ -25807,7 +25805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>2179</v>
       </c>
@@ -25850,7 +25848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>2179</v>
       </c>
@@ -25908,7 +25906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>2179</v>
       </c>
@@ -25966,7 +25964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>2179</v>
       </c>
@@ -26024,7 +26022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>2179</v>
       </c>
@@ -26082,7 +26080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>2179</v>
       </c>
@@ -26140,7 +26138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>2179</v>
       </c>
@@ -26198,7 +26196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>2179</v>
       </c>
@@ -26253,7 +26251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>2179</v>
       </c>
@@ -26311,7 +26309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>2179</v>
       </c>
@@ -26369,7 +26367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>2179</v>
       </c>
@@ -26415,7 +26413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>2179</v>
       </c>
@@ -26473,7 +26471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>2179</v>
       </c>
@@ -26531,7 +26529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>2179</v>
       </c>
@@ -26589,7 +26587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>2179</v>
       </c>
@@ -26647,7 +26645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>2179</v>
       </c>
@@ -26705,7 +26703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>2179</v>
       </c>
@@ -26763,7 +26761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>2179</v>
       </c>
@@ -26821,7 +26819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>2179</v>
       </c>
@@ -26879,7 +26877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>2179</v>
       </c>
@@ -26925,7 +26923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>2179</v>
       </c>
@@ -26983,7 +26981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>2179</v>
       </c>
@@ -27041,7 +27039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>2179</v>
       </c>
@@ -27099,7 +27097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>2179</v>
       </c>
@@ -27157,7 +27155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>2179</v>
       </c>
@@ -27215,7 +27213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>2179</v>
       </c>
@@ -27273,7 +27271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>2179</v>
       </c>
@@ -27331,7 +27329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>2179</v>
       </c>
@@ -27389,7 +27387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>2179</v>
       </c>
@@ -27447,7 +27445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>2179</v>
       </c>
@@ -27505,7 +27503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>2179</v>
       </c>
@@ -27563,7 +27561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>2179</v>
       </c>
@@ -27621,7 +27619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>2179</v>
       </c>
@@ -27679,7 +27677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>2179</v>
       </c>
@@ -27737,7 +27735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>2179</v>
       </c>
@@ -27795,7 +27793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>2179</v>
       </c>
@@ -27853,7 +27851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>2179</v>
       </c>
@@ -27911,7 +27909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>2179</v>
       </c>
@@ -27969,7 +27967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>2179</v>
       </c>
@@ -28027,7 +28025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>2179</v>
       </c>
@@ -28085,7 +28083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>2179</v>
       </c>
@@ -28131,7 +28129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>2179</v>
       </c>
@@ -28189,7 +28187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>2179</v>
       </c>
@@ -28247,7 +28245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>2179</v>
       </c>
@@ -28305,7 +28303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>2179</v>
       </c>
@@ -28363,7 +28361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>2179</v>
       </c>
@@ -28421,7 +28419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>2179</v>
       </c>
@@ -28479,7 +28477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>2179</v>
       </c>
@@ -28537,7 +28535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>2179</v>
       </c>
@@ -28595,7 +28593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>2179</v>
       </c>
@@ -28653,7 +28651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>2179</v>
       </c>
@@ -28699,7 +28697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>2179</v>
       </c>
@@ -28745,7 +28743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>2179</v>
       </c>
@@ -28791,7 +28789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>2179</v>
       </c>
@@ -28837,7 +28835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>2179</v>
       </c>
@@ -28883,7 +28881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>2179</v>
       </c>
@@ -28929,7 +28927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>2179</v>
       </c>
@@ -28975,7 +28973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>2179</v>
       </c>
@@ -29021,7 +29019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>2179</v>
       </c>
@@ -29079,7 +29077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>2179</v>
       </c>
@@ -29137,7 +29135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>2179</v>
       </c>
@@ -29195,7 +29193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>2179</v>
       </c>
@@ -29253,7 +29251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>2179</v>
       </c>
@@ -29311,7 +29309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>2179</v>
       </c>
@@ -29369,7 +29367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>2179</v>
       </c>
@@ -29427,7 +29425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>2179</v>
       </c>
@@ -29485,7 +29483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>2179</v>
       </c>
@@ -29543,7 +29541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>2179</v>
       </c>
@@ -29601,7 +29599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>2179</v>
       </c>
@@ -29659,7 +29657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>2179</v>
       </c>
@@ -29717,7 +29715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>2179</v>
       </c>
@@ -29775,7 +29773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>2179</v>
       </c>
@@ -29833,7 +29831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>2179</v>
       </c>
@@ -29891,7 +29889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>2179</v>
       </c>
@@ -29937,7 +29935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>2179</v>
       </c>
@@ -29995,7 +29993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>2179</v>
       </c>
@@ -30053,7 +30051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>2179</v>
       </c>
@@ -30111,7 +30109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>2179</v>
       </c>
@@ -30169,7 +30167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>2179</v>
       </c>
@@ -30227,7 +30225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>2179</v>
       </c>
@@ -30285,7 +30283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>2179</v>
       </c>
@@ -30343,7 +30341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>2179</v>
       </c>
@@ -30401,7 +30399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>2179</v>
       </c>
@@ -30459,7 +30457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>2179</v>
       </c>
@@ -30517,7 +30515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>2179</v>
       </c>
@@ -30575,7 +30573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>2179</v>
       </c>
@@ -30633,7 +30631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>2179</v>
       </c>
@@ -30691,7 +30689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>2179</v>
       </c>
@@ -30749,7 +30747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>2179</v>
       </c>
@@ -30807,7 +30805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>2179</v>
       </c>
@@ -30865,7 +30863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>2179</v>
       </c>
@@ -30923,7 +30921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>2179</v>
       </c>
@@ -30981,7 +30979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>2179</v>
       </c>
@@ -31039,7 +31037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>2179</v>
       </c>
@@ -31097,7 +31095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>2179</v>
       </c>
@@ -31149,7 +31147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>2179</v>
       </c>
@@ -31207,7 +31205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>2179</v>
       </c>
@@ -31265,7 +31263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>2179</v>
       </c>
@@ -31323,7 +31321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>2179</v>
       </c>
@@ -31381,7 +31379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>2179</v>
       </c>
@@ -31439,7 +31437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>2179</v>
       </c>
@@ -31497,7 +31495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>2179</v>
       </c>
@@ -31555,7 +31553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>2179</v>
       </c>
@@ -31613,7 +31611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>2179</v>
       </c>
@@ -31671,7 +31669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>2179</v>
       </c>
@@ -31729,7 +31727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>2179</v>
       </c>
@@ -31787,7 +31785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>2179</v>
       </c>
@@ -31845,7 +31843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>2179</v>
       </c>
@@ -31903,7 +31901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>2179</v>
       </c>
@@ -31961,7 +31959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>2179</v>
       </c>
@@ -32019,7 +32017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>2179</v>
       </c>
@@ -32062,7 +32060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>2179</v>
       </c>
@@ -32108,7 +32106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>2179</v>
       </c>
@@ -32154,7 +32152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>2179</v>
       </c>
@@ -32212,7 +32210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>2179</v>
       </c>
@@ -32270,7 +32268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>2179</v>
       </c>
@@ -32328,7 +32326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>2179</v>
       </c>
@@ -32386,7 +32384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>2179</v>
       </c>
@@ -32444,7 +32442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>2179</v>
       </c>
@@ -32502,7 +32500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>2179</v>
       </c>
@@ -32560,7 +32558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>2179</v>
       </c>
@@ -32612,7 +32610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>2179</v>
       </c>
@@ -32670,7 +32668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>2179</v>
       </c>
@@ -32722,7 +32720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>2179</v>
       </c>
@@ -32780,7 +32778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>2179</v>
       </c>
@@ -32838,7 +32836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>2179</v>
       </c>
@@ -32896,7 +32894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>2179</v>
       </c>
@@ -32954,7 +32952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>2179</v>
       </c>
@@ -33012,7 +33010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>2179</v>
       </c>
@@ -33070,7 +33068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>2179</v>
       </c>
@@ -33128,7 +33126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>2179</v>
       </c>
@@ -33186,7 +33184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>2179</v>
       </c>
@@ -33244,7 +33242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>2179</v>
       </c>
@@ -33302,7 +33300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>2179</v>
       </c>
@@ -33348,7 +33346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>2179</v>
       </c>
@@ -33406,7 +33404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>2179</v>
       </c>
@@ -33464,7 +33462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>2179</v>
       </c>
@@ -33522,7 +33520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>2179</v>
       </c>
@@ -33580,7 +33578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>2179</v>
       </c>
@@ -33638,7 +33636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>2179</v>
       </c>
@@ -33696,7 +33694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>2179</v>
       </c>
@@ -33754,7 +33752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>2179</v>
       </c>
@@ -33812,7 +33810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>2179</v>
       </c>
@@ -33870,7 +33868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>2179</v>
       </c>
@@ -33928,7 +33926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>2179</v>
       </c>
@@ -33986,7 +33984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>2179</v>
       </c>
@@ -34044,7 +34042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>2179</v>
       </c>
@@ -34102,7 +34100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>2179</v>
       </c>
@@ -34160,7 +34158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>2179</v>
       </c>
@@ -34218,7 +34216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>2179</v>
       </c>
@@ -34276,7 +34274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>2179</v>
       </c>
@@ -34334,7 +34332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>2179</v>
       </c>
@@ -34392,7 +34390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>2179</v>
       </c>
@@ -34450,7 +34448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>2179</v>
       </c>
@@ -34508,7 +34506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>2179</v>
       </c>
@@ -34566,7 +34564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>2179</v>
       </c>
@@ -34624,7 +34622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>2179</v>
       </c>
@@ -34682,7 +34680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>2179</v>
       </c>
@@ -34728,7 +34726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>2179</v>
       </c>
@@ -34786,7 +34784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>2179</v>
       </c>
@@ -34844,7 +34842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>2179</v>
       </c>
@@ -34890,7 +34888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>2179</v>
       </c>
@@ -34948,7 +34946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>2179</v>
       </c>
@@ -35006,7 +35004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>2179</v>
       </c>
@@ -35064,7 +35062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>2179</v>
       </c>
@@ -35122,7 +35120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>2179</v>
       </c>
@@ -35180,7 +35178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>2179</v>
       </c>
@@ -35238,7 +35236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>2179</v>
       </c>
@@ -35296,7 +35294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>2179</v>
       </c>
@@ -35354,7 +35352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>2179</v>
       </c>
@@ -35406,7 +35404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>2179</v>
       </c>
@@ -35464,7 +35462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>2179</v>
       </c>
@@ -35522,7 +35520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>2179</v>
       </c>
@@ -35580,7 +35578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>2179</v>
       </c>
@@ -35638,7 +35636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>2179</v>
       </c>
@@ -35687,7 +35685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>2179</v>
       </c>
@@ -35721,7 +35719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>2179</v>
       </c>
@@ -35764,7 +35762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>2179</v>
       </c>
@@ -35801,7 +35799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>2179</v>
       </c>
@@ -35844,7 +35842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>2179</v>
       </c>
@@ -35878,7 +35876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>2179</v>
       </c>
@@ -35912,7 +35910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>2179</v>
       </c>
@@ -35946,7 +35944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>2179</v>
       </c>
@@ -35989,7 +35987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>2179</v>
       </c>
@@ -36032,7 +36030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>2179</v>
       </c>
@@ -36075,7 +36073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>2179</v>
       </c>
@@ -36118,7 +36116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>2179</v>
       </c>
@@ -36161,7 +36159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>2179</v>
       </c>
@@ -36195,7 +36193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>2179</v>
       </c>
@@ -36238,7 +36236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>2179</v>
       </c>
@@ -36281,7 +36279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>2179</v>
       </c>
@@ -36324,7 +36322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>2179</v>
       </c>
@@ -36367,7 +36365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>2179</v>
       </c>
@@ -36401,7 +36399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>2179</v>
       </c>
@@ -36444,7 +36442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>2179</v>
       </c>
@@ -36487,7 +36485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>2179</v>
       </c>
@@ -36521,7 +36519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>2179</v>
       </c>
@@ -36564,7 +36562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>2179</v>
       </c>
@@ -36607,7 +36605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>2179</v>
       </c>
@@ -36650,7 +36648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>2179</v>
       </c>
@@ -36693,7 +36691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>2180</v>
       </c>
@@ -36751,7 +36749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>2180</v>
       </c>
@@ -36809,7 +36807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>2180</v>
       </c>
@@ -36867,7 +36865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>2180</v>
       </c>
@@ -36913,7 +36911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>2180</v>
       </c>
@@ -36971,7 +36969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>2180</v>
       </c>
@@ -37029,7 +37027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>2180</v>
       </c>
@@ -37087,7 +37085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>2180</v>
       </c>
@@ -37148,7 +37146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>2180</v>
       </c>
@@ -37209,7 +37207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>2180</v>
       </c>
@@ -37270,7 +37268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>2180</v>
       </c>
@@ -37313,7 +37311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>2180</v>
       </c>
@@ -37362,7 +37360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>2180</v>
       </c>
@@ -37414,7 +37412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>2180</v>
       </c>
@@ -37466,7 +37464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>2180</v>
       </c>
@@ -37524,7 +37522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>2180</v>
       </c>
@@ -37582,7 +37580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>2180</v>
       </c>
@@ -37634,7 +37632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>2180</v>
       </c>
@@ -37692,7 +37690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>2180</v>
       </c>
@@ -37750,7 +37748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>2180</v>
       </c>
@@ -37808,7 +37806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>2180</v>
       </c>
@@ -37866,7 +37864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>2180</v>
       </c>
@@ -37924,7 +37922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>2180</v>
       </c>
@@ -37982,7 +37980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>2180</v>
       </c>
@@ -38034,7 +38032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>2180</v>
       </c>
@@ -38092,7 +38090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>2180</v>
       </c>
@@ -38150,7 +38148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>2180</v>
       </c>
@@ -38208,7 +38206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>2180</v>
       </c>
@@ -38266,7 +38264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>2180</v>
       </c>
@@ -38327,7 +38325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>2180</v>
       </c>
@@ -38379,7 +38377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>2180</v>
       </c>
@@ -38440,7 +38438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>2180</v>
       </c>
@@ -38501,7 +38499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>2180</v>
       </c>
@@ -38559,7 +38557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>2180</v>
       </c>
@@ -38611,7 +38609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>2180</v>
       </c>
@@ -38669,7 +38667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>2180</v>
       </c>
@@ -38727,7 +38725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>2180</v>
       </c>
@@ -38785,7 +38783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>2180</v>
       </c>
@@ -38843,7 +38841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>2180</v>
       </c>
@@ -38895,7 +38893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>2180</v>
       </c>
@@ -38953,7 +38951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>2180</v>
       </c>
@@ -39014,7 +39012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>2180</v>
       </c>
@@ -39072,7 +39070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>2180</v>
       </c>
@@ -39124,7 +39122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>2180</v>
       </c>
@@ -39182,7 +39180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>2180</v>
       </c>
@@ -39240,7 +39238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>2180</v>
       </c>
@@ -39301,7 +39299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>2180</v>
       </c>
@@ -39359,7 +39357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>2180</v>
       </c>
@@ -39417,7 +39415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>2180</v>
       </c>
@@ -39475,7 +39473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>2180</v>
       </c>
@@ -39533,7 +39531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>2180</v>
       </c>
@@ -39591,7 +39589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>2180</v>
       </c>
@@ -39649,7 +39647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>2180</v>
       </c>
@@ -39707,7 +39705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>2180</v>
       </c>
@@ -39765,7 +39763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>2180</v>
       </c>
@@ -39823,7 +39821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>2180</v>
       </c>
@@ -39881,7 +39879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>2180</v>
       </c>
@@ -39939,7 +39937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>2180</v>
       </c>
@@ -39997,7 +39995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>2180</v>
       </c>
@@ -40055,7 +40053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>2180</v>
       </c>
@@ -40113,7 +40111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>2180</v>
       </c>
@@ -40174,7 +40172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>2180</v>
       </c>
@@ -40232,7 +40230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>2180</v>
       </c>
@@ -40293,7 +40291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>2180</v>
       </c>
@@ -40351,7 +40349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>2180</v>
       </c>
@@ -40409,7 +40407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>2180</v>
       </c>
@@ -40470,7 +40468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>2180</v>
       </c>
@@ -40528,7 +40526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>2180</v>
       </c>
@@ -40589,7 +40587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>2180</v>
       </c>
@@ -40647,7 +40645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>2180</v>
       </c>
@@ -40705,7 +40703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>2180</v>
       </c>
@@ -40763,7 +40761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>2180</v>
       </c>
@@ -40821,7 +40819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>2180</v>
       </c>
@@ -40879,7 +40877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>2180</v>
       </c>
@@ -40940,7 +40938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>2180</v>
       </c>
@@ -40998,7 +40996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>2180</v>
       </c>
@@ -41056,7 +41054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>2180</v>
       </c>
@@ -41114,7 +41112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>2180</v>
       </c>
@@ -41172,7 +41170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>2180</v>
       </c>
@@ -41230,7 +41228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>2180</v>
       </c>
@@ -41288,7 +41286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>2180</v>
       </c>
@@ -41346,7 +41344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>2180</v>
       </c>
@@ -41404,7 +41402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>2180</v>
       </c>
@@ -41462,7 +41460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>2180</v>
       </c>
@@ -41520,7 +41518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>2180</v>
       </c>
@@ -41578,7 +41576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>2180</v>
       </c>
@@ -41636,7 +41634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>2180</v>
       </c>
@@ -41694,7 +41692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>2180</v>
       </c>
@@ -41752,7 +41750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>2180</v>
       </c>
@@ -41810,7 +41808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>2180</v>
       </c>
@@ -41862,7 +41860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>2180</v>
       </c>
@@ -41920,7 +41918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>2180</v>
       </c>
@@ -41978,7 +41976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>2180</v>
       </c>
@@ -42039,7 +42037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>2180</v>
       </c>
@@ -42100,7 +42098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>2180</v>
       </c>
@@ -42158,7 +42156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>2180</v>
       </c>
@@ -42216,7 +42214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>2180</v>
       </c>
@@ -42277,7 +42275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>2180</v>
       </c>
@@ -42335,7 +42333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>2180</v>
       </c>
@@ -42387,7 +42385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>2180</v>
       </c>
@@ -42445,7 +42443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>2180</v>
       </c>
@@ -42503,7 +42501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>2180</v>
       </c>
@@ -42555,7 +42553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>2180</v>
       </c>
@@ -42604,7 +42602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>2180</v>
       </c>
@@ -42662,7 +42660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>2180</v>
       </c>
@@ -42720,7 +42718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>2180</v>
       </c>
@@ -42781,7 +42779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>2180</v>
       </c>
@@ -42836,7 +42834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>2180</v>
       </c>
@@ -42894,7 +42892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>2180</v>
       </c>
@@ -42952,7 +42950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>2180</v>
       </c>
@@ -43013,7 +43011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>2180</v>
       </c>
@@ -43065,7 +43063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>2180</v>
       </c>
@@ -43123,7 +43121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>2180</v>
       </c>
@@ -43181,7 +43179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>2180</v>
       </c>
@@ -43239,7 +43237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>2180</v>
       </c>
@@ -43297,7 +43295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>2180</v>
       </c>
@@ -43349,7 +43347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>2180</v>
       </c>
@@ -43407,7 +43405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>2180</v>
       </c>
@@ -43465,7 +43463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>2180</v>
       </c>
@@ -43517,7 +43515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>2180</v>
       </c>
@@ -43575,7 +43573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>2180</v>
       </c>
@@ -43633,7 +43631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>2180</v>
       </c>
@@ -43691,7 +43689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>2180</v>
       </c>
@@ -43743,7 +43741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>2180</v>
       </c>
@@ -43801,7 +43799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>2180</v>
       </c>
@@ -43859,7 +43857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>2180</v>
       </c>
@@ -43917,7 +43915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>2180</v>
       </c>
@@ -43975,7 +43973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>2180</v>
       </c>
@@ -44033,7 +44031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>2180</v>
       </c>
@@ -44085,7 +44083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>2180</v>
       </c>
@@ -44140,7 +44138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>2180</v>
       </c>
@@ -44192,7 +44190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>2180</v>
       </c>
@@ -44247,7 +44245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>2180</v>
       </c>
@@ -44305,7 +44303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>2180</v>
       </c>
@@ -44357,7 +44355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>2180</v>
       </c>
@@ -44415,7 +44413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>2180</v>
       </c>
@@ -44470,7 +44468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>2180</v>
       </c>
@@ -44528,7 +44526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>2180</v>
       </c>
@@ -44580,7 +44578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>2180</v>
       </c>
@@ -44638,7 +44636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>2180</v>
       </c>
@@ -44754,7 +44752,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="397" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>2180</v>
       </c>
@@ -44812,7 +44810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>2180</v>
       </c>
@@ -44870,7 +44868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>2180</v>
       </c>
@@ -44922,7 +44920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="400" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>2180</v>
       </c>
@@ -44980,7 +44978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>2180</v>
       </c>
@@ -45038,7 +45036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>2180</v>
       </c>
@@ -45096,7 +45094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>2180</v>
       </c>
@@ -45154,7 +45152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>2180</v>
       </c>
@@ -45212,7 +45210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>2180</v>
       </c>
@@ -45270,7 +45268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>2180</v>
       </c>
@@ -45328,7 +45326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>2180</v>
       </c>
@@ -45386,7 +45384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>2180</v>
       </c>
@@ -45444,7 +45442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>2180</v>
       </c>
@@ -45502,7 +45500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>2180</v>
       </c>
@@ -45560,7 +45558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>2180</v>
       </c>
@@ -45615,7 +45613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>2180</v>
       </c>
@@ -45673,7 +45671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>2180</v>
       </c>
@@ -45731,7 +45729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>2180</v>
       </c>
@@ -45786,7 +45784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>2180</v>
       </c>
@@ -45844,7 +45842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>2180</v>
       </c>
@@ -45902,7 +45900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>2180</v>
       </c>
@@ -45960,7 +45958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>2180</v>
       </c>
@@ -46015,7 +46013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>2180</v>
       </c>
@@ -46073,7 +46071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>2180</v>
       </c>
@@ -46131,7 +46129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>2180</v>
       </c>
@@ -46189,7 +46187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>2180</v>
       </c>
@@ -46250,7 +46248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>2180</v>
       </c>
@@ -46311,7 +46309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>2180</v>
       </c>
@@ -46372,7 +46370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>2180</v>
       </c>
@@ -46430,7 +46428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>2180</v>
       </c>
@@ -46488,7 +46486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>2180</v>
       </c>
@@ -46546,7 +46544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>2180</v>
       </c>
@@ -46598,7 +46596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>2180</v>
       </c>
@@ -46656,7 +46654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>2180</v>
       </c>
@@ -46714,7 +46712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>2180</v>
       </c>
@@ -46772,7 +46770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>2180</v>
       </c>
@@ -46833,7 +46831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>2180</v>
       </c>
@@ -46891,7 +46889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>2180</v>
       </c>
@@ -46952,7 +46950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>2180</v>
       </c>
@@ -47004,7 +47002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="436" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>2180</v>
       </c>
@@ -47056,7 +47054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>2180</v>
       </c>
@@ -47108,7 +47106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="438" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>2180</v>
       </c>
@@ -47218,7 +47216,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="440" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>2180</v>
       </c>
@@ -47270,7 +47268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>2180</v>
       </c>
@@ -47325,7 +47323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>2180</v>
       </c>
@@ -47383,7 +47381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>2180</v>
       </c>
@@ -47438,7 +47436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>2180</v>
       </c>
@@ -47551,7 +47549,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="446" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>2180</v>
       </c>
@@ -47609,7 +47607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>2180</v>
       </c>
@@ -47661,7 +47659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>2180</v>
       </c>
@@ -47719,7 +47717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>2180</v>
       </c>
@@ -47777,7 +47775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>2180</v>
       </c>
@@ -47835,7 +47833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>2180</v>
       </c>
@@ -47887,7 +47885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="452" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>2180</v>
       </c>
@@ -47945,7 +47943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>2180</v>
       </c>
@@ -48003,7 +48001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>2180</v>
       </c>
@@ -48052,7 +48050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="455" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>2180</v>
       </c>
@@ -48107,7 +48105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>2180</v>
       </c>
@@ -48165,7 +48163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>2180</v>
       </c>
@@ -48223,7 +48221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>2180</v>
       </c>
@@ -48281,7 +48279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>2180</v>
       </c>
@@ -48339,7 +48337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>2180</v>
       </c>
@@ -48397,7 +48395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>2180</v>
       </c>
@@ -48455,7 +48453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>2180</v>
       </c>
@@ -48516,7 +48514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>2180</v>
       </c>
@@ -48574,7 +48572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>2180</v>
       </c>
@@ -48632,7 +48630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>2180</v>
       </c>
@@ -48687,7 +48685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>2180</v>
       </c>
@@ -48745,7 +48743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>2180</v>
       </c>
@@ -48803,7 +48801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>2180</v>
       </c>
@@ -48861,7 +48859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>2180</v>
       </c>
@@ -48916,7 +48914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>2180</v>
       </c>
@@ -48968,7 +48966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="471" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>2180</v>
       </c>
@@ -49026,7 +49024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>2180</v>
       </c>
@@ -49078,7 +49076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="473" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>2180</v>
       </c>
@@ -49136,7 +49134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>2180</v>
       </c>
@@ -49197,7 +49195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>2180</v>
       </c>
@@ -49243,7 +49241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="476" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>2180</v>
       </c>
@@ -49301,7 +49299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>2180</v>
       </c>
@@ -49359,7 +49357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>2180</v>
       </c>
@@ -49417,7 +49415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>2180</v>
       </c>
@@ -49475,68 +49473,68 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A480" s="5" t="s">
+    <row r="480" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
         <v>2180</v>
       </c>
-      <c r="B480" s="5" t="s">
+      <c r="B480" t="s">
         <v>926</v>
       </c>
-      <c r="C480" s="5" t="s">
+      <c r="C480" t="s">
         <v>927</v>
       </c>
-      <c r="D480" s="5" t="s">
+      <c r="D480" t="s">
         <v>1880</v>
       </c>
-      <c r="E480" s="5" t="s">
+      <c r="E480" t="s">
         <v>1430</v>
       </c>
-      <c r="F480" s="5" t="s">
+      <c r="F480" t="s">
         <v>1430</v>
       </c>
-      <c r="G480" s="5">
-        <v>0</v>
-      </c>
-      <c r="H480" s="5">
+      <c r="G480">
+        <v>0</v>
+      </c>
+      <c r="H480">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="I480" s="5">
+      <c r="I480">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J480" s="5">
+      <c r="J480">
         <v>70</v>
       </c>
-      <c r="L480" s="5" t="s">
+      <c r="L480" t="s">
         <v>2189</v>
       </c>
-      <c r="M480" s="5">
-        <v>1</v>
-      </c>
-      <c r="N480" s="5">
+      <c r="M480">
+        <v>1</v>
+      </c>
+      <c r="N480">
         <v>3</v>
       </c>
-      <c r="O480" s="5">
-        <v>1</v>
-      </c>
-      <c r="P480" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q480" s="5">
-        <v>1</v>
-      </c>
-      <c r="R480" s="5">
-        <v>0</v>
-      </c>
-      <c r="S480" s="5">
-        <v>0</v>
-      </c>
-      <c r="T480" s="5" t="s">
+      <c r="O480">
+        <v>1</v>
+      </c>
+      <c r="P480">
+        <v>1</v>
+      </c>
+      <c r="Q480">
+        <v>1</v>
+      </c>
+      <c r="R480">
+        <v>0</v>
+      </c>
+      <c r="S480">
+        <v>0</v>
+      </c>
+      <c r="T480" t="s">
         <v>2186</v>
       </c>
     </row>
-    <row r="481" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>2180</v>
       </c>
@@ -49597,7 +49595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>2180</v>
       </c>
@@ -49655,7 +49653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>2180</v>
       </c>
@@ -49701,7 +49699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="484" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>2180</v>
       </c>
@@ -49759,7 +49757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>2180</v>
       </c>
@@ -49817,7 +49815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>2180</v>
       </c>
@@ -49875,7 +49873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>2180</v>
       </c>
@@ -49927,7 +49925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>2180</v>
       </c>
@@ -49979,7 +49977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>2180</v>
       </c>
@@ -50037,7 +50035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>2180</v>
       </c>
@@ -50095,7 +50093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>2180</v>
       </c>
@@ -50150,7 +50148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>2180</v>
       </c>
@@ -50208,7 +50206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>2180</v>
       </c>
@@ -50260,7 +50258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="494" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>2180</v>
       </c>
@@ -50306,7 +50304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="495" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>2180</v>
       </c>
@@ -50349,7 +50347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="496" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>2181</v>
       </c>
@@ -50407,7 +50405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>2181</v>
       </c>
@@ -50465,7 +50463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>2181</v>
       </c>
@@ -50523,7 +50521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>2181</v>
       </c>
@@ -50581,7 +50579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>2181</v>
       </c>
@@ -50639,7 +50637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>2181</v>
       </c>
@@ -50685,7 +50683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="502" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>2181</v>
       </c>
@@ -50743,7 +50741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>2181</v>
       </c>
@@ -50789,7 +50787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>2181</v>
       </c>
@@ -50847,7 +50845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>2181</v>
       </c>
@@ -50905,7 +50903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>2181</v>
       </c>
@@ -50963,7 +50961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>2181</v>
       </c>
@@ -51021,7 +51019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>2181</v>
       </c>
@@ -51079,7 +51077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>2181</v>
       </c>
@@ -51125,7 +51123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>2181</v>
       </c>
@@ -51183,7 +51181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>2181</v>
       </c>
@@ -51241,7 +51239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>2181</v>
       </c>
@@ -51299,7 +51297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>2181</v>
       </c>
@@ -51357,7 +51355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>2181</v>
       </c>
@@ -51415,7 +51413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>2181</v>
       </c>
@@ -51473,7 +51471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>2181</v>
       </c>
@@ -51531,7 +51529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>2181</v>
       </c>
@@ -51589,7 +51587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>2181</v>
       </c>
@@ -51647,7 +51645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>2181</v>
       </c>
@@ -51705,7 +51703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>2181</v>
       </c>
@@ -51763,7 +51761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>2181</v>
       </c>
@@ -51821,7 +51819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>2181</v>
       </c>
@@ -51876,7 +51874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>2181</v>
       </c>
@@ -51934,7 +51932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>2181</v>
       </c>
@@ -51980,7 +51978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>2181</v>
       </c>
@@ -52026,7 +52024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="526" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>2181</v>
       </c>
@@ -52084,7 +52082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>2181</v>
       </c>
@@ -52142,7 +52140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>2181</v>
       </c>
@@ -52200,7 +52198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>2181</v>
       </c>
@@ -52258,7 +52256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>2181</v>
       </c>
@@ -52304,7 +52302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>2181</v>
       </c>
@@ -52356,7 +52354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>2181</v>
       </c>
@@ -52414,7 +52412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>2181</v>
       </c>
@@ -52472,7 +52470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>2181</v>
       </c>
@@ -52530,7 +52528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>2181</v>
       </c>
@@ -52576,7 +52574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>2181</v>
       </c>
@@ -52631,7 +52629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>2181</v>
       </c>
@@ -52689,7 +52687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>2181</v>
       </c>
@@ -52747,7 +52745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>2181</v>
       </c>
@@ -52799,7 +52797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="540" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>2181</v>
       </c>
@@ -52857,7 +52855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>2181</v>
       </c>
@@ -52915,7 +52913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>2181</v>
       </c>
@@ -52973,7 +52971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>2181</v>
       </c>
@@ -53028,7 +53026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>2181</v>
       </c>
@@ -53083,7 +53081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>2181</v>
       </c>
@@ -53138,7 +53136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>2181</v>
       </c>
@@ -53196,7 +53194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>2181</v>
       </c>
@@ -53254,7 +53252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>2181</v>
       </c>
@@ -53312,7 +53310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>2181</v>
       </c>
@@ -53370,7 +53368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>2181</v>
       </c>
@@ -53428,7 +53426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>2181</v>
       </c>
@@ -53483,7 +53481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>2181</v>
       </c>
@@ -53538,7 +53536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>2181</v>
       </c>
@@ -53593,7 +53591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>2181</v>
       </c>
@@ -53651,7 +53649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>2181</v>
       </c>
@@ -53709,7 +53707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="556" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>2181</v>
       </c>
@@ -53764,7 +53762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>2181</v>
       </c>
@@ -53807,7 +53805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="558" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>2181</v>
       </c>
@@ -53862,7 +53860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>2181</v>
       </c>
@@ -53917,7 +53915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>2181</v>
       </c>
@@ -53969,7 +53967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="561" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>2181</v>
       </c>
@@ -54027,7 +54025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>2181</v>
       </c>
@@ -54085,7 +54083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>2181</v>
       </c>
@@ -54131,7 +54129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="564" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>2181</v>
       </c>
@@ -54189,7 +54187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>2181</v>
       </c>
@@ -54241,7 +54239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="566" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>2181</v>
       </c>
@@ -54299,7 +54297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>2181</v>
       </c>
@@ -54357,7 +54355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>2181</v>
       </c>
@@ -54415,7 +54413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>2181</v>
       </c>
@@ -54473,7 +54471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>2181</v>
       </c>
@@ -54531,7 +54529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>2181</v>
       </c>
@@ -54589,7 +54587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>2181</v>
       </c>
@@ -54647,7 +54645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>2181</v>
       </c>
@@ -54702,7 +54700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>2181</v>
       </c>
@@ -54754,7 +54752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>2181</v>
       </c>
@@ -54812,7 +54810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>2181</v>
       </c>
@@ -54870,7 +54868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>2181</v>
       </c>
@@ -54928,7 +54926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>2181</v>
       </c>
@@ -54986,7 +54984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>2181</v>
       </c>
@@ -55044,7 +55042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>2181</v>
       </c>
@@ -55102,7 +55100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>2181</v>
       </c>
@@ -55160,7 +55158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>2181</v>
       </c>
@@ -55218,7 +55216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>2181</v>
       </c>
@@ -55270,7 +55268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="584" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>2181</v>
       </c>
@@ -55328,7 +55326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>2181</v>
       </c>
@@ -55386,7 +55384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>2181</v>
       </c>
@@ -55444,7 +55442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="587" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>2181</v>
       </c>
@@ -55502,7 +55500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="588" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>2181</v>
       </c>
@@ -55560,7 +55558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="589" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>2181</v>
       </c>
@@ -55618,7 +55616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="590" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>2181</v>
       </c>
@@ -55676,7 +55674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>2181</v>
       </c>
@@ -55734,7 +55732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>2181</v>
       </c>
@@ -55792,7 +55790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>2181</v>
       </c>
@@ -55850,7 +55848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>2181</v>
       </c>
@@ -55908,7 +55906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>2181</v>
       </c>
@@ -55966,7 +55964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="596" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>2181</v>
       </c>
@@ -56024,7 +56022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="597" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>2181</v>
       </c>
@@ -56070,7 +56068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>2181</v>
       </c>
@@ -56128,7 +56126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="599" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>2181</v>
       </c>
@@ -56186,7 +56184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>2181</v>
       </c>
@@ -56244,7 +56242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>2181</v>
       </c>
@@ -56302,7 +56300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>2181</v>
       </c>
@@ -56360,7 +56358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>2181</v>
       </c>
@@ -56418,7 +56416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="604" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>2181</v>
       </c>
@@ -56476,7 +56474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="605" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>2181</v>
       </c>
@@ -56534,7 +56532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="606" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>2181</v>
       </c>
@@ -56586,7 +56584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="607" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>2181</v>
       </c>
@@ -56644,7 +56642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="608" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>2181</v>
       </c>
@@ -56702,7 +56700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="609" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>2181</v>
       </c>
@@ -56754,7 +56752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="610" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>2181</v>
       </c>
@@ -56812,7 +56810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="611" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>2181</v>
       </c>
@@ -56864,7 +56862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="612" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>2181</v>
       </c>
@@ -56922,7 +56920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>2181</v>
       </c>
@@ -56980,7 +56978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="614" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>2181</v>
       </c>
@@ -57038,7 +57036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="615" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>2181</v>
       </c>
@@ -57096,7 +57094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>2181</v>
       </c>
@@ -57154,7 +57152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>2181</v>
       </c>
@@ -57206,7 +57204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="618" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>2181</v>
       </c>
@@ -57264,7 +57262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>2181</v>
       </c>
@@ -57322,7 +57320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="620" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>2181</v>
       </c>
@@ -57380,7 +57378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>2181</v>
       </c>
@@ -57438,7 +57436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="622" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>2181</v>
       </c>
@@ -57496,7 +57494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="623" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>2181</v>
       </c>
@@ -57554,7 +57552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="624" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>2181</v>
       </c>
@@ -57612,7 +57610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>2181</v>
       </c>
@@ -57670,7 +57668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="626" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>2181</v>
       </c>
@@ -57728,7 +57726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>2181</v>
       </c>
@@ -57786,7 +57784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>2181</v>
       </c>
@@ -57844,7 +57842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="629" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>2181</v>
       </c>
@@ -57902,7 +57900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="630" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>2181</v>
       </c>
@@ -57957,7 +57955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="631" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>2181</v>
       </c>
@@ -58012,7 +58010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="632" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>2181</v>
       </c>
@@ -58070,7 +58068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="633" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>2181</v>
       </c>
@@ -58125,7 +58123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="634" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>2181</v>
       </c>
@@ -58180,7 +58178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="635" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>2181</v>
       </c>
@@ -58238,7 +58236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="636" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>2181</v>
       </c>
@@ -58296,7 +58294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="637" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>2181</v>
       </c>
@@ -58354,7 +58352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="638" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>2181</v>
       </c>
@@ -58412,7 +58410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="639" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>2181</v>
       </c>
@@ -58470,7 +58468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="640" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>2181</v>
       </c>
@@ -58528,7 +58526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="641" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>2181</v>
       </c>
@@ -58586,7 +58584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="642" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>2181</v>
       </c>
@@ -58644,7 +58642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>2181</v>
       </c>
@@ -58702,7 +58700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>2181</v>
       </c>
@@ -58760,7 +58758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>2181</v>
       </c>
@@ -58812,7 +58810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="646" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>2181</v>
       </c>
@@ -58870,7 +58868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="647" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>2181</v>
       </c>
@@ -58928,7 +58926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="648" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>2181</v>
       </c>
@@ -58986,7 +58984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="649" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>2181</v>
       </c>
@@ -59044,7 +59042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="650" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>2181</v>
       </c>
@@ -59102,7 +59100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>2181</v>
       </c>
@@ -59154,7 +59152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="652" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>2181</v>
       </c>
@@ -59212,7 +59210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="653" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>2181</v>
       </c>
@@ -59270,7 +59268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="654" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>2181</v>
       </c>
@@ -59328,7 +59326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="655" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>2181</v>
       </c>
@@ -59386,7 +59384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="656" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>2181</v>
       </c>
@@ -59444,7 +59442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="657" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>2181</v>
       </c>
@@ -59502,7 +59500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="658" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>2181</v>
       </c>
@@ -59560,7 +59558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="659" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>2181</v>
       </c>
@@ -59606,7 +59604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="660" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>2181</v>
       </c>
@@ -59664,7 +59662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="661" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>2181</v>
       </c>
@@ -59722,7 +59720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="662" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>2181</v>
       </c>
@@ -59780,7 +59778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="663" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>2181</v>
       </c>
@@ -59838,7 +59836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="664" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>2181</v>
       </c>
@@ -59896,7 +59894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="665" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>2181</v>
       </c>
@@ -59954,7 +59952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="666" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>2181</v>
       </c>
@@ -60000,7 +59998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="667" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>2181</v>
       </c>
@@ -60058,7 +60056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="668" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>2181</v>
       </c>
@@ -60110,7 +60108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="669" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>2181</v>
       </c>
@@ -60168,7 +60166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="670" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>2181</v>
       </c>
@@ -60226,7 +60224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="671" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>2181</v>
       </c>
@@ -60284,7 +60282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="672" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>2181</v>
       </c>
@@ -60339,7 +60337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="673" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>2181</v>
       </c>
@@ -60397,7 +60395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="674" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>2181</v>
       </c>
@@ -60455,7 +60453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="675" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>2181</v>
       </c>
@@ -60513,7 +60511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="676" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>2181</v>
       </c>
@@ -60571,7 +60569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="677" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>2181</v>
       </c>
@@ -60690,7 +60688,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="679" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>2181</v>
       </c>
@@ -60748,7 +60746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="680" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>2181</v>
       </c>
@@ -60806,7 +60804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>2181</v>
       </c>
@@ -60864,7 +60862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="682" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>2181</v>
       </c>
@@ -60922,7 +60920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="683" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>2181</v>
       </c>
@@ -60980,7 +60978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="684" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>2181</v>
       </c>
@@ -61038,7 +61036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="685" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>2181</v>
       </c>
@@ -61096,7 +61094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="686" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>2181</v>
       </c>
@@ -61154,7 +61152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="687" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>2181</v>
       </c>
@@ -61206,7 +61204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="688" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>2181</v>
       </c>
@@ -61264,7 +61262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="689" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>2181</v>
       </c>
@@ -61322,7 +61320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="690" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>2181</v>
       </c>
@@ -61380,7 +61378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="691" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>2181</v>
       </c>
@@ -61438,7 +61436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="692" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>2181</v>
       </c>
@@ -61496,7 +61494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="693" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>2181</v>
       </c>
@@ -61554,7 +61552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="694" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>2181</v>
       </c>
@@ -61612,7 +61610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="695" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>2181</v>
       </c>
@@ -61670,7 +61668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="696" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>2181</v>
       </c>
@@ -61728,7 +61726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="697" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>2181</v>
       </c>
@@ -61774,7 +61772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="698" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>2181</v>
       </c>
@@ -61829,7 +61827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="699" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>2181</v>
       </c>
@@ -61887,7 +61885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="700" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>2181</v>
       </c>
@@ -61945,7 +61943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="701" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>2181</v>
       </c>
@@ -62000,7 +61998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="702" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>2181</v>
       </c>
@@ -62058,7 +62056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="703" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>2181</v>
       </c>
@@ -62116,7 +62114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="704" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>2181</v>
       </c>
@@ -62174,7 +62172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="705" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>2181</v>
       </c>
@@ -62220,7 +62218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="706" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>2181</v>
       </c>
@@ -62278,7 +62276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="707" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>2181</v>
       </c>
@@ -62336,7 +62334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>2181</v>
       </c>
@@ -62394,7 +62392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="709" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>2181</v>
       </c>
@@ -62440,7 +62438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="710" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>2181</v>
       </c>
@@ -62498,7 +62496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="711" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>2181</v>
       </c>
@@ -62556,7 +62554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="712" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>2181</v>
       </c>
@@ -62614,7 +62612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="713" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>2181</v>
       </c>
@@ -62672,7 +62670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="714" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>2181</v>
       </c>
@@ -62727,7 +62725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="715" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>2181</v>
       </c>
@@ -62785,7 +62783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="716" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>2181</v>
       </c>
@@ -62843,7 +62841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="717" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>2181</v>
       </c>
@@ -62901,7 +62899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="718" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>2181</v>
       </c>
@@ -62950,7 +62948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="719" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>2181</v>
       </c>
@@ -63005,7 +63003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="720" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>2181</v>
       </c>
@@ -63063,7 +63061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="721" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>2181</v>
       </c>
@@ -63115,7 +63113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="722" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>2181</v>
       </c>
@@ -63173,7 +63171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="723" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>2181</v>
       </c>
@@ -63231,7 +63229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="724" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>2181</v>
       </c>
@@ -63289,7 +63287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="725" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>2181</v>
       </c>
@@ -63347,7 +63345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="726" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>2181</v>
       </c>
@@ -63405,7 +63403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="727" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>2181</v>
       </c>
@@ -63463,7 +63461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="728" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>2181</v>
       </c>
@@ -63518,7 +63516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="729" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>2181</v>
       </c>
@@ -63567,7 +63565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="730" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>2181</v>
       </c>
@@ -63623,13 +63621,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T730" xr:uid="{0FAB02E2-8283-44DB-BC1E-88DE8C1F843E}">
-    <filterColumn colId="19">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:T731">
     <cfRule type="expression" dxfId="0" priority="3">
